--- a/uat-test-plans-reduced30/G2-16258-fe-plp-content-blocks.xlsx
+++ b/uat-test-plans-reduced30/G2-16258-fe-plp-content-blocks.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced ~30% — 7/10 checks retained, lowest-priority sections dropped] 11 UI-testable stories mapped to 10 business checklist checks and 11 coverage rows. 10 linked BO/QA/hub stories/tasks were excluded as non-customer-facing capability scope.</t>
+          <t>[Reduced V2 ~0% — 10/10 checks retained; AC and core-case coverage guardrails enforced] 11 UI-testable stories mapped to 10 business checklist checks and 11 coverage rows. 10 linked BO/QA/hub stories/tasks were excluded as non-customer-facing capability scope.</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=12306; payload_chars=12302; est_tokens~3076; checklist_rows=7; matrix_rows=8; exploratory_rows=3</t>
+          <t>payload_bytes=15059; payload_chars=15055; est_tokens~3764; checklist_rows=10; matrix_rows=11; exploratory_rows=3</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
@@ -1028,6 +1028,113 @@
       </c>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>UAT-008</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Kozlova, Nika || External</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Content Block Text Binding</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Mochi content block text/link field alignment is preserved in storefront output</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Validate a content block configured with text in CMS and confirm matching text/link rendering in PLP components that consume Mochi payload.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Rendered call-to-action text matches configured CMS text field semantics.
+No legacy field mismatch causes missing or incorrect link labels.</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="79" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>UAT-009</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Kozlova, Nika || External</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Content Stories Extended Assets</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Content stories support optional middle and closing cover assets</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>1. On configured PLPs, verify carousel with mandatory cover and optional middle/closing covers.
+2. Confirm optionality behavior when secondary assets are absent.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Mandatory cover always renders.
+Optional middle and closing covers render only when provided and do not break carousel flow.
+Desktop and mobile behavior remains stable.</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>UAT-010</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Kozlova, Nika || External</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Cross-Service Propagation</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>New cover assets propagate from CMS source to storefront consumer services</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Publish updated content stories assets and verify downstream storefront consumption path reflects new assets for both brands.</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Published assets are propagated and rendered in expected consumer flow.
+No stale asset payload appears after publish/update cycle.</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1040,19 +1147,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -1540,6 +1647,169 @@
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>COV-009</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>G2-23000</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>AC-LinkText-Alignment</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Mochi linkText/text field alignment for content-block labels</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>UAT-008</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Commits 6ffd3aa and d02298f in mytheresa/mochi.</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>No explicit acceptance criteria are present in Jira description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>COV-010</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>G2-23127</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>AC-Stories-Optional-Covers</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Support optional middle/closing covers in content stories carousel</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>UAT-009</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Commit 03e5ff0 in mytheresa/atelier.</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>COV-011</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>G2-23132</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>AC-Propagation-Hyena</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Propagation of additional cover assets through Hyena consumer path</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>UAT-010</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Commits 0a89c2d and 7e52e5d in mytheresa/hyena.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/uat-test-plans-reduced30/G2-16258-fe-plp-content-blocks.xlsx
+++ b/uat-test-plans-reduced30/G2-16258-fe-plp-content-blocks.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced V2 ~0% — 10/10 checks retained; AC and core-case coverage guardrails enforced] 11 UI-testable stories mapped to 10 business checklist checks and 11 coverage rows. 10 linked BO/QA/hub stories/tasks were excluded as non-customer-facing capability scope.</t>
+          <t>[Reduced V2 ~0% — 10/10 checks retained; AC coverage guardrail enforced] 11 UI-testable stories mapped to 10 business checklist checks and 11 coverage rows. 10 linked BO/QA/hub stories/tasks were excluded as non-customer-facing capability scope.</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=15059; payload_chars=15055; est_tokens~3764; checklist_rows=10; matrix_rows=11; exploratory_rows=3</t>
+          <t>payload_bytes=15044; payload_chars=15040; est_tokens~3760; checklist_rows=10; matrix_rows=11; exploratory_rows=3</t>
         </is>
       </c>
     </row>
